--- a/artfynd/A 61129-2024 artfynd.xlsx
+++ b/artfynd/A 61129-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031918</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 61129-2024 artfynd.xlsx
+++ b/artfynd/A 61129-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 61129-2024 artfynd.xlsx
+++ b/artfynd/A 61129-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122031918</v>
+        <v>122031479</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2869</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496449</v>
+        <v>496561</v>
       </c>
       <c r="R2" t="n">
-        <v>6624488</v>
+        <v>6624129</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -778,6 +778,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122031918</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>496449</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6624488</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
